--- a/docs/AD210/AD210_UT_정기점검계획_v2.xlsx
+++ b/docs/AD210/AD210_UT_정기점검계획_v2.xlsx
@@ -3757,7 +3757,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>"오늘 및 최종작업 완료일 이후로 생성" 안내 후 저장되지 않음</t>
+          <t>지난 날짜도 계획이 생성됨 (사양 확인 2026-10-21: 팝업 안내는 권고, 생성 허용)</t>
         </is>
       </c>
       <c r="H58" s="10">
@@ -6812,23 +6812,14 @@
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>오류</t>
-        </is>
-      </c>
-      <c r="J58" s="33" t="inlineStr">
-        <is>
-          <t>일정추가 계획일자 칸의 달력에서 어제(2026-10-20)가 선택 가능 → 저장 시 '처리되었습니다', 작업계획 생성됨.
-→ 기대: 오늘·최종 완료일 이후만 생성 (팝업 안내 문구와 다름)</t>
-        </is>
-      </c>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="J58" s="33" t="inlineStr"/>
       <c r="K58" s="51" t="n">
         <v>46315</v>
       </c>
-      <c r="L58" s="5" t="inlineStr">
-        <is>
-          <t>ad210-EC_002-calendar.png, ad210-EC_002.png</t>
-        </is>
-      </c>
+      <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="6" t="n"/>
       <c r="N58" s="6" t="n"/>
       <c r="O58" s="6" t="n"/>
